--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.43936016670689</v>
+        <v>4.783896027089869</v>
       </c>
       <c r="D2" t="n">
-        <v>28.81259391184737</v>
+        <v>4.682046510675198</v>
       </c>
       <c r="E2" t="n">
-        <v>16.20977064991315</v>
+        <v>2.634087730610886</v>
       </c>
       <c r="F2" t="n">
-        <v>3.600838975268827</v>
+        <v>0.5851363334811843</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.85890146653318</v>
+        <v>10.05207148831164</v>
       </c>
       <c r="D3" t="n">
-        <v>36.01427186238502</v>
+        <v>5.852319177637566</v>
       </c>
       <c r="E3" t="n">
-        <v>16.20977064991315</v>
+        <v>2.634087730610886</v>
       </c>
       <c r="F3" t="n">
-        <v>3.600838975268827</v>
+        <v>0.5851363334811843</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
